--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486547_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486547_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7173</v>
+        <v>2.4897</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7494</v>
+        <v>0.6372</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0321</v>
+        <v>1.8525</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2905</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.0803</v>
+        <v>0.3344</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7897</v>
+        <v>0.4001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.8956</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.7789</v>
+        <v>0.2222</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2966</v>
+        <v>0.6734</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8082</v>
+        <v>-0.1611</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3013</v>
+        <v>0.1122</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5068</v>
+        <v>-0.2733</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1802</v>
+        <v>-0.3545</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2318</v>
+        <v>-0.2584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9485</v>
+        <v>-0.0961</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4438</v>
+        <v>1.0227</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4715</v>
+        <v>0.9928</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0277</v>
+        <v>0.0299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2233</v>
+        <v>-1.092</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0585</v>
+        <v>-0.359</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8351</v>
+        <v>-0.7331</v>
       </c>
       <c r="J3" t="n">
-        <v>3.121</v>
+        <v>-0.1732</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8532</v>
+        <v>0.073</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2677</v>
+        <v>-0.2462</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.8976</v>
+        <v>-0.9188</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7948</v>
+        <v>-0.432</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1029</v>
+        <v>-0.4869</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>3.22</v>
+        <v>-0.1027</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7219</v>
+        <v>0.0361</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4981</v>
+        <v>-0.1388</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4345</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.2838</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2258</v>
+        <v>0.5249</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2569</v>
+        <v>5.6503</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4827</v>
+        <v>-5.1254</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7344000000000001</v>
+        <v>1.1819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3344</v>
+        <v>1.0129</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4001</v>
+        <v>0.1689</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8956</v>
+        <v>4.2922</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2222</v>
+        <v>2.7223</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6734</v>
+        <v>1.5698</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1611</v>
+        <v>-3.1103</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1122</v>
+        <v>-1.7094</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2733</v>
+        <v>-1.4009</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6184</v>
+        <v>0.603</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1524</v>
+        <v>0.7931</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.466</v>
+        <v>-0.1902</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3698</v>
+        <v>-1.695</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3698</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8178</v>
+        <v>0.5228</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0973</v>
+        <v>1.0789</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.2795</v>
+        <v>-0.5561</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1819</v>
+        <v>-0.2905</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0129</v>
+        <v>-2.0803</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1689</v>
+        <v>1.7897</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2922</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7223</v>
+        <v>-1.7789</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5698</v>
+        <v>2.2966</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1103</v>
+        <v>-0.8082</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7094</v>
+        <v>-0.3013</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4009</v>
+        <v>-0.5068</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8959</v>
+        <v>0.9857</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2402</v>
+        <v>0.5612</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3443</v>
+        <v>0.4245</v>
       </c>
       <c r="V5" t="n">
         <v>-1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2599</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6373</v>
+        <v>-0.5982</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5458</v>
+        <v>-0.4068</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0915</v>
+        <v>-0.1914</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.092</v>
+        <v>-1.0019</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.359</v>
+        <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7331</v>
+        <v>-1.0933</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1732</v>
+        <v>0.1003</v>
       </c>
       <c r="K6" t="n">
-        <v>0.073</v>
+        <v>0.9402</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2462</v>
+        <v>-0.8399</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9188</v>
+        <v>-1.1022</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.432</v>
+        <v>-0.8488</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>-0.2534</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4881</v>
+        <v>0.469</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>0.5804</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0772</v>
+        <v>-0.1115</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.09</v>
+        <v>-1.0302</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2779</v>
+        <v>1.4598</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3678</v>
+        <v>-2.49</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.2233</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0944</v>
+        <v>1.0585</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1833</v>
+        <v>-0.8351</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6116</v>
+        <v>3.121</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0944</v>
+        <v>2.8532</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5172</v>
+        <v>0.2677</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7004</v>
+        <v>-2.8976</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.7948</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7004</v>
+        <v>-1.1029</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4111</v>
+        <v>0.746</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4711</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06</v>
+        <v>0.0357</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0647</v>
+        <v>-2.4345</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>-1.2838</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2599</v>
+        <v>-1.1507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2725</v>
+        <v>-1.2826</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.742</v>
+        <v>1.0544</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5305</v>
+        <v>-2.337</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0019</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0914</v>
+        <v>0.0944</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0933</v>
+        <v>-0.1833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1003</v>
+        <v>0.6116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9402</v>
+        <v>0.0944</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8399</v>
+        <v>0.5172</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1022</v>
+        <v>-0.7004</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8488</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2534</v>
+        <v>-0.7004</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2054</v>
+        <v>0.2184</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2452</v>
+        <v>0.2476</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4505</v>
+        <v>-0.0291</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3698</v>
+        <v>-2.0647</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3698</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8634</v>
+        <v>-3.4722</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2203</v>
+        <v>-1.7675</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.643</v>
+        <v>-1.7047</v>
       </c>
       <c r="G9" t="n">
         <v>-4.4956</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1731</v>
+        <v>0.2181</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1849</v>
+        <v>0.268</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0118</v>
+        <v>-0.0499</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9347</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.3322</v>
+        <v>-7.2282</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6673</v>
+        <v>-3.7791</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6649</v>
+        <v>-3.4491</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5956</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7435</v>
+        <v>0.8475</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8532</v>
+        <v>0.7415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1097</v>
+        <v>0.106</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.0442</v>
+        <v>-7.7089</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5456</v>
+        <v>-5.2104</v>
       </c>
       <c r="F11" t="n">
         <v>-2.4985</v>
@@ -1312,10 +1312,10 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0601</v>
+        <v>0.3954</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1334</v>
+        <v>0.2019</v>
       </c>
       <c r="U11" t="n">
         <v>0.1935</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.7603</v>
+        <v>-16.7602</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2902000000000013</v>
+        <v>-0.2904</v>
       </c>
       <c r="F12" t="n">
         <v>-16.4698</v>
@@ -1375,7 +1375,7 @@
         <v>-20.0822</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.476099999999999</v>
+        <v>-9.476100000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-10.6062</v>
@@ -1390,16 +1390,16 @@
         <v>10.8752</v>
       </c>
       <c r="S12" t="n">
-        <v>4.0258</v>
+        <v>4.0259</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8817</v>
+        <v>3.881600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1442</v>
+        <v>0.1441</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.410000000000001</v>
+        <v>-6.41</v>
       </c>
       <c r="W12" t="n">
         <v>0.9968999999999997</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2285</v>
+        <v>5.1348</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2873</v>
+        <v>4.092</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0588</v>
+        <v>1.0429</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2611</v>
+        <v>4.9129</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1479</v>
+        <v>2.7645</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1131</v>
+        <v>2.1483</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7513</v>
+        <v>4.2445</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5983</v>
+        <v>2.5033</v>
       </c>
       <c r="L13" t="n">
-        <v>0.153</v>
+        <v>1.7412</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4902</v>
+        <v>0.6684</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4504</v>
+        <v>0.2612</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0399</v>
+        <v>0.4072</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0996</v>
+        <v>-1.038</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7557</v>
+        <v>-0.0204</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6561</v>
+        <v>-1.0175</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9554</v>
+        <v>1.695</v>
       </c>
       <c r="W13" t="n">
         <v>0.9554</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9274</v>
+        <v>4.7449</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6449</v>
+        <v>5.8253</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2825</v>
+        <v>-1.0803</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9129</v>
+        <v>8.0952</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7645</v>
+        <v>-0.2009</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1483</v>
+        <v>8.296099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2445</v>
+        <v>8.956799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5033</v>
+        <v>-0.0151</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7412</v>
+        <v>8.9719</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6684</v>
+        <v>-0.8616</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2612</v>
+        <v>-0.1858</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4072</v>
+        <v>-0.6758</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2454</v>
+        <v>-0.2274</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4675</v>
+        <v>-0.1947</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7779</v>
+        <v>-0.0328</v>
       </c>
       <c r="V14" t="n">
-        <v>1.695</v>
+        <v>-1.6003</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9554</v>
+        <v>-0.5443</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7395</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4874</v>
+        <v>3.4962</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2665</v>
+        <v>2.1095</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7791</v>
+        <v>1.3867</v>
       </c>
       <c r="G15" t="n">
-        <v>8.0952</v>
+        <v>1.7575</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2009</v>
+        <v>0.0881</v>
       </c>
       <c r="I15" t="n">
-        <v>8.296099999999999</v>
+        <v>1.6694</v>
       </c>
       <c r="J15" t="n">
-        <v>8.956799999999999</v>
+        <v>1.3352</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0151</v>
+        <v>0.073</v>
       </c>
       <c r="L15" t="n">
-        <v>8.9719</v>
+        <v>1.2622</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8616</v>
+        <v>0.4222</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1858</v>
+        <v>0.0151</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6758</v>
+        <v>0.4072</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4849</v>
+        <v>-0.1178</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1382</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7315</v>
+        <v>0.0204</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6003</v>
+        <v>1.2039</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5443</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.056</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4347</v>
+        <v>3.2972</v>
       </c>
       <c r="E16" t="n">
-        <v>2.473</v>
+        <v>3.058</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9617</v>
+        <v>0.2392</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5717</v>
+        <v>3.2611</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6538</v>
+        <v>3.1479</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.1131</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6324</v>
+        <v>3.7513</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4412</v>
+        <v>3.5983</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1912</v>
+        <v>0.153</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0607</v>
+        <v>-0.4902</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2127</v>
+        <v>-0.4504</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2733</v>
+        <v>-0.0399</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3991</v>
+        <v>0.1682</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8857</v>
+        <v>0.5264</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5135</v>
+        <v>-0.3581</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3339</v>
+        <v>0.9554</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>0.9554</v>
       </c>
       <c r="X16" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3125</v>
+        <v>2.5382</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4448</v>
+        <v>1.8024</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8678</v>
+        <v>0.7358</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7575</v>
+        <v>0.5717</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0881</v>
+        <v>0.6538</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6694</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3352</v>
+        <v>0.6324</v>
       </c>
       <c r="K17" t="n">
-        <v>0.073</v>
+        <v>0.4412</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2622</v>
+        <v>0.1912</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4222</v>
+        <v>-0.0607</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0151</v>
+        <v>0.2127</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4072</v>
+        <v>-0.2733</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3014</v>
+        <v>0.5026</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1971</v>
+        <v>0.2151</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4985</v>
+        <v>0.2875</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2039</v>
+        <v>2.3339</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X17" t="n">
         <v>0.074</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3605</v>
+        <v>1.7445</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0534</v>
+        <v>1.1651</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3071</v>
+        <v>0.5794</v>
       </c>
       <c r="G18" t="n">
         <v>0.7971</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6629</v>
+        <v>-0.2788</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.536</v>
+        <v>-0.4242</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1269</v>
+        <v>0.1454</v>
       </c>
       <c r="V18" t="n">
         <v>1.0087</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9125</v>
+        <v>1.5034</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3411</v>
+        <v>1.7881</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4286</v>
+        <v>-0.2847</v>
       </c>
       <c r="G19" t="n">
         <v>1.4658</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8154</v>
+        <v>-0.2244</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2674</v>
+        <v>-0.1235</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3904</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7833</v>
+        <v>0.3363</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9133</v>
+        <v>1.4662</v>
       </c>
       <c r="F20" t="n">
         <v>-1.13</v>
@@ -2014,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.447</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7451</v>
+        <v>0.298</v>
       </c>
       <c r="U20" t="n">
         <v>-0.298</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3635</v>
+        <v>0.1299</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.606</v>
+        <v>-1.159</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2425</v>
+        <v>1.2889</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1404</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5928</v>
+        <v>-0.0994</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0448</v>
+        <v>0.0015</v>
       </c>
       <c r="V21" t="n">
         <v>0.3698</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7562</v>
+        <v>-0.3156</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.823</v>
+        <v>-0.7113</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0668</v>
+        <v>0.3956</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9239000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.68</v>
+        <v>-0.2394</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2091</v>
+        <v>0.3209</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8892</v>
+        <v>-0.5603</v>
       </c>
       <c r="V22" t="n">
         <v>0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2531</v>
+        <v>-0.5389</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9087</v>
+        <v>-1.4617</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4639</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5157</v>
+        <v>0.1986</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.3749</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3063</v>
+        <v>0.5735</v>
       </c>
       <c r="V23" t="n">
         <v>0.074</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3139</v>
+        <v>-2.3305</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6166</v>
+        <v>-1.5048</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6973</v>
+        <v>-0.8257</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4658</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.327</v>
+        <v>0.3103</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.262</v>
+        <v>-0.1502</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5889</v>
+        <v>0.4605</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.7601</v>
+        <v>19.74039999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>16.47</v>
+        <v>16.4698</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2903000000000002</v>
+        <v>3.2707</v>
       </c>
       <c r="G25" t="n">
         <v>17.6386</v>
@@ -2404,13 +2404,13 @@
         <v>7.612500000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.0258</v>
+        <v>-1.0455</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1443</v>
+        <v>-0.144</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.8816</v>
+        <v>-0.9013999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>6.4102</v>
@@ -2419,7 +2419,7 @@
         <v>7.4068</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.9966999999999999</v>
+        <v>-0.9966999999999997</v>
       </c>
     </row>
   </sheetData>
